--- a/human-assess/human_assess.xlsx
+++ b/human-assess/human_assess.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pyprojects_now\PythonProject\bli\test\generation-human-compare\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\学习\研一\LLM\问卷设计\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363110A8-3B6E-472F-AA80-DC601823372A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B27FFC9-E037-484A-8AC5-588F2853049B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="repo-out" sheetId="9" r:id="rId1"/>
@@ -22,14 +22,14 @@
     <sheet name="Sheet13" sheetId="13" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'func-out'!$B$1:$H$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'func-out'!$B$1:$G$145</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1267" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="388">
   <si>
     <t>assess</t>
   </si>
@@ -1302,9 +1302,6 @@
   </si>
   <si>
     <t>order</t>
-  </si>
-  <si>
-    <t>prompt</t>
   </si>
   <si>
     <t>comment</t>
@@ -6128,15 +6125,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0B95DA-0835-48EF-8EE8-432D9DB46016}">
-  <dimension ref="A1:O145"/>
+  <dimension ref="A1:N145"/>
   <sheetFormatPr defaultColWidth="15.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="5" max="5" width="15.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>323</v>
@@ -6157,31 +6154,28 @@
         <v>325</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>326</v>
+        <v>6</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="7" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:14">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -6195,40 +6189,37 @@
         <v>108</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="F2" s="4">
-        <v>3</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>329</v>
+      <c r="H2" s="7">
+        <v>1</v>
       </c>
       <c r="I2" s="7">
         <v>1</v>
       </c>
       <c r="J2" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" s="7">
-        <v>1</v>
-      </c>
-      <c r="O2" s="7">
         <v>0.46666666666666667</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -6242,40 +6233,37 @@
         <v>108</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="F3" s="4">
-        <v>3</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>329</v>
+      <c r="H3" s="7">
+        <v>3</v>
       </c>
       <c r="I3" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L3" s="7">
         <v>4</v>
       </c>
       <c r="M3" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N3" s="7">
-        <v>3</v>
-      </c>
-      <c r="O3" s="7">
         <v>0.7</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:14">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -6289,40 +6277,37 @@
         <v>108</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="F4" s="7">
-        <v>3</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>329</v>
+      <c r="H4" s="7">
+        <v>2</v>
       </c>
       <c r="I4" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L4" s="7">
         <v>3</v>
       </c>
       <c r="M4" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4" s="7">
-        <v>2</v>
-      </c>
-      <c r="O4" s="7">
         <v>0.56666666666666665</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:14">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -6336,22 +6321,22 @@
         <v>108</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="F5" s="7">
-        <v>0</v>
+        <v>329</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H5" s="7" t="s">
         <v>110</v>
       </c>
+      <c r="H5" s="7">
+        <v>5</v>
+      </c>
       <c r="I5" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5" s="7">
         <v>5</v>
@@ -6363,13 +6348,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="7">
-        <v>5</v>
-      </c>
-      <c r="O5" s="7">
         <v>0.96666666666666667</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:14">
       <c r="A6" s="7">
         <v>2</v>
       </c>
@@ -6383,40 +6365,37 @@
         <v>108</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="F6" s="7">
-        <v>0</v>
+        <v>329</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H6" s="7" t="s">
         <v>110</v>
       </c>
+      <c r="H6" s="7">
+        <v>5</v>
+      </c>
       <c r="I6" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L6" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M6" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N6" s="7">
-        <v>4</v>
-      </c>
-      <c r="O6" s="7">
         <v>0.9</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:14">
       <c r="A7" s="7">
         <v>3</v>
       </c>
@@ -6430,22 +6409,22 @@
         <v>108</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="F7" s="7">
-        <v>0</v>
+        <v>329</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="H7" s="7" t="s">
         <v>110</v>
       </c>
+      <c r="H7" s="7">
+        <v>4</v>
+      </c>
       <c r="I7" s="7">
         <v>4</v>
       </c>
       <c r="J7" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K7" s="7">
         <v>5</v>
@@ -6457,13 +6436,10 @@
         <v>5</v>
       </c>
       <c r="N7" s="7">
-        <v>5</v>
-      </c>
-      <c r="O7" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="7">
         <v>1</v>
       </c>
@@ -6477,22 +6453,22 @@
         <v>108</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="F8" s="7">
-        <v>0</v>
+        <v>330</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H8" s="7" t="s">
         <v>113</v>
       </c>
+      <c r="H8" s="7">
+        <v>5</v>
+      </c>
       <c r="I8" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J8" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K8" s="7">
         <v>5</v>
@@ -6501,16 +6477,13 @@
         <v>5</v>
       </c>
       <c r="M8" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N8" s="7">
-        <v>3</v>
-      </c>
-      <c r="O8" s="7">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="7">
         <v>2</v>
       </c>
@@ -6524,40 +6497,37 @@
         <v>108</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="F9" s="7">
-        <v>0</v>
+        <v>330</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H9" s="7" t="s">
         <v>113</v>
       </c>
+      <c r="H9" s="7">
+        <v>5</v>
+      </c>
       <c r="I9" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9" s="7">
         <v>4</v>
       </c>
       <c r="K9" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9" s="7">
         <v>5</v>
       </c>
       <c r="M9" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N9" s="7">
-        <v>4</v>
-      </c>
-      <c r="O9" s="7">
         <v>0.9</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="A10" s="7">
         <v>3</v>
       </c>
@@ -6571,40 +6541,37 @@
         <v>108</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="F10" s="7">
-        <v>0</v>
+        <v>330</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H10" s="7" t="s">
         <v>113</v>
       </c>
+      <c r="H10" s="7">
+        <v>5</v>
+      </c>
       <c r="I10" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J10" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K10" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L10" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N10" s="7">
-        <v>3</v>
-      </c>
-      <c r="O10" s="7">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="7">
         <v>1</v>
       </c>
@@ -6618,40 +6585,37 @@
         <v>91</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="F11" s="7">
-        <v>0</v>
+        <v>331</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="H11" s="7" t="s">
         <v>93</v>
       </c>
+      <c r="H11" s="7">
+        <v>4</v>
+      </c>
       <c r="I11" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J11" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K11" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L11" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M11" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N11" s="7">
-        <v>2</v>
-      </c>
-      <c r="O11" s="7">
         <v>0.6333333333333333</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:14">
       <c r="A12" s="7">
         <v>2</v>
       </c>
@@ -6665,22 +6629,22 @@
         <v>91</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="F12" s="7">
-        <v>0</v>
+        <v>331</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="7" t="s">
         <v>93</v>
       </c>
+      <c r="H12" s="7">
+        <v>4</v>
+      </c>
       <c r="I12" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K12" s="7">
         <v>5</v>
@@ -6689,16 +6653,13 @@
         <v>5</v>
       </c>
       <c r="M12" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N12" s="7">
-        <v>3</v>
-      </c>
-      <c r="O12" s="7">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:14">
       <c r="A13" s="7">
         <v>3</v>
       </c>
@@ -6712,40 +6673,37 @@
         <v>91</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="F13" s="7">
-        <v>0</v>
+        <v>331</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="7" t="s">
         <v>93</v>
       </c>
+      <c r="H13" s="7">
+        <v>4</v>
+      </c>
       <c r="I13" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K13" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L13" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M13" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N13" s="7">
-        <v>3</v>
-      </c>
-      <c r="O13" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:14">
       <c r="A14" s="7">
         <v>1</v>
       </c>
@@ -6759,22 +6717,22 @@
         <v>91</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="F14" s="7">
-        <v>0</v>
+        <v>332</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H14" s="7" t="s">
         <v>95</v>
       </c>
+      <c r="H14" s="7">
+        <v>4</v>
+      </c>
       <c r="I14" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K14" s="7">
         <v>5</v>
@@ -6783,16 +6741,13 @@
         <v>5</v>
       </c>
       <c r="M14" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14" s="7">
-        <v>4</v>
-      </c>
-      <c r="O14" s="7">
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:14">
       <c r="A15" s="7">
         <v>2</v>
       </c>
@@ -6806,22 +6761,22 @@
         <v>91</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="F15" s="7">
-        <v>0</v>
+        <v>332</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H15" s="7" t="s">
         <v>95</v>
       </c>
+      <c r="H15" s="7">
+        <v>4</v>
+      </c>
       <c r="I15" s="7">
         <v>4</v>
       </c>
       <c r="J15" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="7">
         <v>5</v>
@@ -6830,16 +6785,13 @@
         <v>5</v>
       </c>
       <c r="M15" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N15" s="7">
-        <v>4</v>
-      </c>
-      <c r="O15" s="7">
         <v>0.9</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:14">
       <c r="A16" s="7">
         <v>3</v>
       </c>
@@ -6853,40 +6805,37 @@
         <v>91</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="F16" s="7">
-        <v>0</v>
+        <v>332</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H16" s="7" t="s">
         <v>95</v>
       </c>
+      <c r="H16" s="7">
+        <v>4</v>
+      </c>
       <c r="I16" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J16" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L16" s="7">
         <v>5</v>
       </c>
       <c r="M16" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N16" s="7">
-        <v>4</v>
-      </c>
-      <c r="O16" s="7">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:14">
       <c r="A17" s="7">
         <v>1</v>
       </c>
@@ -6902,17 +6851,17 @@
       <c r="E17" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="7">
-        <v>0</v>
+      <c r="F17" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H17" s="7" t="s">
         <v>98</v>
       </c>
+      <c r="H17" s="7">
+        <v>4</v>
+      </c>
       <c r="I17" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J17" s="7">
         <v>5</v>
@@ -6927,13 +6876,10 @@
         <v>5</v>
       </c>
       <c r="N17" s="7">
-        <v>5</v>
-      </c>
-      <c r="O17" s="7">
         <v>0.96666666666666667</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:14">
       <c r="A18" s="7">
         <v>2</v>
       </c>
@@ -6949,20 +6895,20 @@
       <c r="E18" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F18" s="7">
-        <v>0</v>
+      <c r="F18" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H18" s="7" t="s">
         <v>98</v>
       </c>
+      <c r="H18" s="7">
+        <v>4</v>
+      </c>
       <c r="I18" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J18" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K18" s="7">
         <v>5</v>
@@ -6971,16 +6917,13 @@
         <v>5</v>
       </c>
       <c r="M18" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N18" s="7">
-        <v>4</v>
-      </c>
-      <c r="O18" s="7">
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:14">
       <c r="A19" s="7">
         <v>3</v>
       </c>
@@ -6996,38 +6939,35 @@
       <c r="E19" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="7">
-        <v>0</v>
+      <c r="F19" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H19" s="7" t="s">
         <v>98</v>
       </c>
+      <c r="H19" s="7">
+        <v>5</v>
+      </c>
       <c r="I19" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J19" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K19" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L19" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M19" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N19" s="7">
-        <v>4</v>
-      </c>
-      <c r="O19" s="7">
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:14">
       <c r="A20" s="7">
         <v>1</v>
       </c>
@@ -7041,17 +6981,17 @@
         <v>43</v>
       </c>
       <c r="E20" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="F20" s="7">
-        <v>0</v>
-      </c>
       <c r="G20" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="H20" s="7" t="s">
         <v>104</v>
       </c>
+      <c r="H20" s="7">
+        <v>5</v>
+      </c>
       <c r="I20" s="7">
         <v>5</v>
       </c>
@@ -7068,13 +7008,10 @@
         <v>5</v>
       </c>
       <c r="N20" s="7">
-        <v>5</v>
-      </c>
-      <c r="O20" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="7">
         <v>2</v>
       </c>
@@ -7088,40 +7025,37 @@
         <v>43</v>
       </c>
       <c r="E21" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="F21" s="7">
-        <v>0</v>
-      </c>
       <c r="G21" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="H21" s="7" t="s">
         <v>104</v>
       </c>
+      <c r="H21" s="7">
+        <v>5</v>
+      </c>
       <c r="I21" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J21" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K21" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L21" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M21" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N21" s="7">
-        <v>4</v>
-      </c>
-      <c r="O21" s="7">
         <v>0.9</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:14">
       <c r="A22" s="7">
         <v>3</v>
       </c>
@@ -7135,22 +7069,22 @@
         <v>43</v>
       </c>
       <c r="E22" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="F22" s="7">
-        <v>0</v>
-      </c>
       <c r="G22" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="H22" s="7" t="s">
         <v>104</v>
       </c>
+      <c r="H22" s="7">
+        <v>4</v>
+      </c>
       <c r="I22" s="7">
         <v>4</v>
       </c>
       <c r="J22" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="7">
         <v>5</v>
@@ -7162,13 +7096,10 @@
         <v>5</v>
       </c>
       <c r="N22" s="7">
-        <v>5</v>
-      </c>
-      <c r="O22" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:14">
       <c r="A23" s="7">
         <v>1</v>
       </c>
@@ -7182,19 +7113,19 @@
         <v>43</v>
       </c>
       <c r="E23" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="F23" s="7">
-        <v>0</v>
-      </c>
       <c r="G23" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="H23" s="7" t="s">
         <v>105</v>
       </c>
+      <c r="H23" s="7">
+        <v>4</v>
+      </c>
       <c r="I23" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="7">
         <v>5</v>
@@ -7209,13 +7140,10 @@
         <v>5</v>
       </c>
       <c r="N23" s="7">
-        <v>5</v>
-      </c>
-      <c r="O23" s="7">
         <v>0.96666666666666667</v>
       </c>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:14">
       <c r="A24" s="7">
         <v>2</v>
       </c>
@@ -7229,22 +7157,22 @@
         <v>43</v>
       </c>
       <c r="E24" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="F24" s="7">
-        <v>0</v>
-      </c>
       <c r="G24" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="H24" s="7" t="s">
         <v>105</v>
       </c>
+      <c r="H24" s="7">
+        <v>4</v>
+      </c>
       <c r="I24" s="7">
         <v>4</v>
       </c>
       <c r="J24" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K24" s="7">
         <v>5</v>
@@ -7256,13 +7184,10 @@
         <v>5</v>
       </c>
       <c r="N24" s="7">
-        <v>5</v>
-      </c>
-      <c r="O24" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:14">
       <c r="A25" s="7">
         <v>3</v>
       </c>
@@ -7276,40 +7201,37 @@
         <v>43</v>
       </c>
       <c r="E25" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="F25" s="7">
-        <v>0</v>
-      </c>
       <c r="G25" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="H25" s="7" t="s">
         <v>105</v>
       </c>
+      <c r="H25" s="7">
+        <v>4</v>
+      </c>
       <c r="I25" s="7">
         <v>4</v>
       </c>
       <c r="J25" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K25" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L25" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M25" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N25" s="7">
-        <v>4</v>
-      </c>
-      <c r="O25" s="7">
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:14">
       <c r="A26" s="7">
         <v>1</v>
       </c>
@@ -7323,22 +7245,22 @@
         <v>43</v>
       </c>
       <c r="E26" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="F26" s="7">
-        <v>0</v>
-      </c>
       <c r="G26" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H26" s="7" t="s">
         <v>106</v>
       </c>
+      <c r="H26" s="7">
+        <v>5</v>
+      </c>
       <c r="I26" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J26" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K26" s="7">
         <v>5</v>
@@ -7347,16 +7269,13 @@
         <v>5</v>
       </c>
       <c r="M26" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N26" s="7">
-        <v>3</v>
-      </c>
-      <c r="O26" s="7">
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:14">
       <c r="A27" s="7">
         <v>2</v>
       </c>
@@ -7370,22 +7289,22 @@
         <v>43</v>
       </c>
       <c r="E27" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="F27" s="7">
-        <v>0</v>
-      </c>
       <c r="G27" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H27" s="7" t="s">
         <v>106</v>
       </c>
+      <c r="H27" s="7">
+        <v>4</v>
+      </c>
       <c r="I27" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J27" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" s="7">
         <v>5</v>
@@ -7394,16 +7313,13 @@
         <v>5</v>
       </c>
       <c r="M27" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N27" s="7">
-        <v>4</v>
-      </c>
-      <c r="O27" s="7">
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:14">
       <c r="A28" s="7">
         <v>3</v>
       </c>
@@ -7417,40 +7333,37 @@
         <v>43</v>
       </c>
       <c r="E28" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="F28" s="7">
-        <v>0</v>
-      </c>
       <c r="G28" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="H28" s="7" t="s">
         <v>106</v>
       </c>
+      <c r="H28" s="7">
+        <v>4</v>
+      </c>
       <c r="I28" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J28" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K28" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L28" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M28" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N28" s="7">
-        <v>4</v>
-      </c>
-      <c r="O28" s="7">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:14">
       <c r="A29" s="7">
         <v>1</v>
       </c>
@@ -7464,22 +7377,22 @@
         <v>76</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="F29" s="7">
-        <v>0</v>
+        <v>339</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="H29" s="7" t="s">
         <v>85</v>
       </c>
+      <c r="H29" s="7">
+        <v>4</v>
+      </c>
       <c r="I29" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J29" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K29" s="7">
         <v>5</v>
@@ -7488,16 +7401,13 @@
         <v>5</v>
       </c>
       <c r="M29" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N29" s="7">
-        <v>3</v>
-      </c>
-      <c r="O29" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:14">
       <c r="A30" s="7">
         <v>2</v>
       </c>
@@ -7511,40 +7421,37 @@
         <v>76</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="F30" s="7">
-        <v>0</v>
+        <v>339</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="H30" s="7" t="s">
         <v>85</v>
       </c>
+      <c r="H30" s="7">
+        <v>4</v>
+      </c>
       <c r="I30" s="7">
         <v>4</v>
       </c>
       <c r="J30" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L30" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M30" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N30" s="7">
-        <v>4</v>
-      </c>
-      <c r="O30" s="7">
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:14">
       <c r="A31" s="7">
         <v>3</v>
       </c>
@@ -7558,40 +7465,37 @@
         <v>76</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="F31" s="7">
-        <v>0</v>
+        <v>339</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="H31" s="7" t="s">
         <v>85</v>
       </c>
+      <c r="H31" s="7">
+        <v>5</v>
+      </c>
       <c r="I31" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J31" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="7">
         <v>4</v>
       </c>
       <c r="L31" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M31" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N31" s="7">
-        <v>3</v>
-      </c>
-      <c r="O31" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:14">
       <c r="A32" s="7">
         <v>1</v>
       </c>
@@ -7605,22 +7509,22 @@
         <v>76</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="F32" s="7">
-        <v>0</v>
+        <v>340</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H32" s="7" t="s">
         <v>87</v>
       </c>
+      <c r="H32" s="7">
+        <v>4</v>
+      </c>
       <c r="I32" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J32" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K32" s="7">
         <v>5</v>
@@ -7629,16 +7533,13 @@
         <v>5</v>
       </c>
       <c r="M32" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N32" s="7">
-        <v>3</v>
-      </c>
-      <c r="O32" s="7">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:14">
       <c r="A33" s="7">
         <v>2</v>
       </c>
@@ -7652,40 +7553,37 @@
         <v>76</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="F33" s="7">
-        <v>0</v>
+        <v>340</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H33" s="7" t="s">
         <v>87</v>
       </c>
+      <c r="H33" s="7">
+        <v>4</v>
+      </c>
       <c r="I33" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J33" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K33" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L33" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M33" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N33" s="7">
-        <v>4</v>
-      </c>
-      <c r="O33" s="7">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:14">
       <c r="A34" s="7">
         <v>3</v>
       </c>
@@ -7699,40 +7597,37 @@
         <v>76</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="F34" s="7">
-        <v>0</v>
+        <v>340</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H34" s="7" t="s">
         <v>87</v>
       </c>
+      <c r="H34" s="7">
+        <v>4</v>
+      </c>
       <c r="I34" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J34" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K34" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L34" s="7">
         <v>5</v>
       </c>
       <c r="M34" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N34" s="7">
-        <v>3</v>
-      </c>
-      <c r="O34" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:14">
       <c r="A35" s="7">
         <v>1</v>
       </c>
@@ -7746,40 +7641,37 @@
         <v>76</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="F35" s="7">
-        <v>0</v>
+        <v>341</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H35" s="7" t="s">
         <v>89</v>
       </c>
+      <c r="H35" s="7">
+        <v>2</v>
+      </c>
       <c r="I35" s="7">
         <v>2</v>
       </c>
       <c r="J35" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K35" s="7">
         <v>4</v>
       </c>
       <c r="L35" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M35" s="7">
         <v>2</v>
       </c>
       <c r="N35" s="7">
-        <v>2</v>
-      </c>
-      <c r="O35" s="7">
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:14">
       <c r="A36" s="7">
         <v>2</v>
       </c>
@@ -7793,40 +7685,37 @@
         <v>76</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="F36" s="7">
-        <v>0</v>
+        <v>341</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H36" s="7" t="s">
         <v>89</v>
       </c>
+      <c r="H36" s="7">
+        <v>4</v>
+      </c>
       <c r="I36" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J36" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K36" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L36" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M36" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N36" s="7">
-        <v>3</v>
-      </c>
-      <c r="O36" s="7">
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:14">
       <c r="A37" s="7">
         <v>3</v>
       </c>
@@ -7840,40 +7729,37 @@
         <v>76</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="F37" s="7">
-        <v>0</v>
+        <v>341</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H37" s="7" t="s">
         <v>89</v>
       </c>
+      <c r="H37" s="7">
+        <v>4</v>
+      </c>
       <c r="I37" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J37" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K37" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L37" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M37" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N37" s="7">
-        <v>2</v>
-      </c>
-      <c r="O37" s="7">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:14">
       <c r="A38" s="7">
         <v>1</v>
       </c>
@@ -7887,40 +7773,37 @@
         <v>76</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="F38" s="7">
-        <v>0</v>
+        <v>342</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="H38" s="7" t="s">
         <v>82</v>
       </c>
+      <c r="H38" s="7">
+        <v>3</v>
+      </c>
       <c r="I38" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J38" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K38" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L38" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M38" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N38" s="7">
-        <v>3</v>
-      </c>
-      <c r="O38" s="7">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
+    <row r="39" spans="1:14">
       <c r="A39" s="7">
         <v>2</v>
       </c>
@@ -7934,40 +7817,37 @@
         <v>76</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="F39" s="7">
-        <v>0</v>
+        <v>342</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="H39" s="7" t="s">
         <v>82</v>
       </c>
+      <c r="H39" s="7">
+        <v>4</v>
+      </c>
       <c r="I39" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J39" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K39" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L39" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M39" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N39" s="7">
-        <v>3</v>
-      </c>
-      <c r="O39" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
+    <row r="40" spans="1:14">
       <c r="A40" s="7">
         <v>3</v>
       </c>
@@ -7981,40 +7861,37 @@
         <v>76</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="F40" s="7">
-        <v>0</v>
+        <v>342</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="H40" s="7" t="s">
         <v>82</v>
       </c>
+      <c r="H40" s="7">
+        <v>5</v>
+      </c>
       <c r="I40" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J40" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K40" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L40" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M40" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N40" s="7">
-        <v>2</v>
-      </c>
-      <c r="O40" s="7">
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
+    <row r="41" spans="1:14">
       <c r="A41" s="7">
         <v>1</v>
       </c>
@@ -8028,22 +7905,22 @@
         <v>76</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="F41" s="7">
-        <v>0</v>
+        <v>343</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H41" s="7" t="s">
         <v>80</v>
       </c>
+      <c r="H41" s="7">
+        <v>3</v>
+      </c>
       <c r="I41" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J41" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K41" s="7">
         <v>5</v>
@@ -8052,16 +7929,13 @@
         <v>5</v>
       </c>
       <c r="M41" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N41" s="7">
-        <v>3</v>
-      </c>
-      <c r="O41" s="7">
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
+    <row r="42" spans="1:14">
       <c r="A42" s="7">
         <v>2</v>
       </c>
@@ -8075,40 +7949,37 @@
         <v>76</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="F42" s="7">
-        <v>0</v>
+        <v>343</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H42" s="7" t="s">
         <v>80</v>
       </c>
+      <c r="H42" s="7">
+        <v>4</v>
+      </c>
       <c r="I42" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J42" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K42" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L42" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M42" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N42" s="7">
-        <v>4</v>
-      </c>
-      <c r="O42" s="7">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
+    <row r="43" spans="1:14">
       <c r="A43" s="7">
         <v>3</v>
       </c>
@@ -8122,40 +7993,37 @@
         <v>76</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="F43" s="7">
-        <v>0</v>
+        <v>343</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H43" s="7" t="s">
         <v>80</v>
       </c>
+      <c r="H43" s="7">
+        <v>4</v>
+      </c>
       <c r="I43" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J43" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K43" s="7">
         <v>4</v>
       </c>
       <c r="L43" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M43" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N43" s="7">
-        <v>3</v>
-      </c>
-      <c r="O43" s="7">
         <v>0.73333333333333328</v>
       </c>
     </row>
-    <row r="44" spans="1:15">
+    <row r="44" spans="1:14">
       <c r="A44" s="7">
         <v>1</v>
       </c>
@@ -8169,22 +8037,22 @@
         <v>76</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="F44" s="7">
-        <v>0</v>
+        <v>344</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H44" s="7" t="s">
         <v>78</v>
       </c>
+      <c r="H44" s="7">
+        <v>3</v>
+      </c>
       <c r="I44" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J44" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K44" s="7">
         <v>5</v>
@@ -8193,16 +8061,13 @@
         <v>5</v>
       </c>
       <c r="M44" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N44" s="7">
-        <v>3</v>
-      </c>
-      <c r="O44" s="7">
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" spans="1:14">
       <c r="A45" s="7">
         <v>2</v>
       </c>
@@ -8216,40 +8081,37 @@
         <v>76</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="F45" s="7">
-        <v>0</v>
+        <v>344</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H45" s="7" t="s">
         <v>78</v>
       </c>
+      <c r="H45" s="7">
+        <v>4</v>
+      </c>
       <c r="I45" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J45" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K45" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L45" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M45" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N45" s="7">
-        <v>3</v>
-      </c>
-      <c r="O45" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:14">
       <c r="A46" s="7">
         <v>3</v>
       </c>
@@ -8263,40 +8125,37 @@
         <v>76</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="F46" s="7">
-        <v>0</v>
+        <v>344</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H46" s="7" t="s">
         <v>78</v>
       </c>
+      <c r="H46" s="7">
+        <v>4</v>
+      </c>
       <c r="I46" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J46" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K46" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L46" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M46" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N46" s="7">
-        <v>2</v>
-      </c>
-      <c r="O46" s="7">
         <v>0.73333333333333328</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" spans="1:14">
       <c r="A47" s="7">
         <v>1</v>
       </c>
@@ -8310,22 +8169,22 @@
         <v>51</v>
       </c>
       <c r="E47" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="F47" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="F47" s="7">
-        <v>0</v>
-      </c>
       <c r="G47" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="H47" s="7" t="s">
         <v>100</v>
       </c>
+      <c r="H47" s="7">
+        <v>5</v>
+      </c>
       <c r="I47" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J47" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K47" s="7">
         <v>5</v>
@@ -8334,16 +8193,13 @@
         <v>5</v>
       </c>
       <c r="M47" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N47" s="7">
-        <v>4</v>
-      </c>
-      <c r="O47" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:14">
       <c r="A48" s="7">
         <v>2</v>
       </c>
@@ -8357,22 +8213,22 @@
         <v>51</v>
       </c>
       <c r="E48" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="F48" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="F48" s="7">
-        <v>0</v>
-      </c>
       <c r="G48" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="H48" s="7" t="s">
         <v>100</v>
       </c>
+      <c r="H48" s="7">
+        <v>5</v>
+      </c>
       <c r="I48" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J48" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K48" s="7">
         <v>5</v>
@@ -8381,16 +8237,13 @@
         <v>5</v>
       </c>
       <c r="M48" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N48" s="7">
-        <v>4</v>
-      </c>
-      <c r="O48" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:14">
       <c r="A49" s="7">
         <v>3</v>
       </c>
@@ -8404,22 +8257,22 @@
         <v>51</v>
       </c>
       <c r="E49" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="F49" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="F49" s="7">
-        <v>0</v>
-      </c>
       <c r="G49" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="H49" s="7" t="s">
         <v>100</v>
       </c>
+      <c r="H49" s="7">
+        <v>4</v>
+      </c>
       <c r="I49" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J49" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K49" s="7">
         <v>5</v>
@@ -8428,16 +8281,13 @@
         <v>5</v>
       </c>
       <c r="M49" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N49" s="7">
-        <v>4</v>
-      </c>
-      <c r="O49" s="7">
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:14">
       <c r="A50" s="7">
         <v>1</v>
       </c>
@@ -8451,40 +8301,37 @@
         <v>51</v>
       </c>
       <c r="E50" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="F50" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="F50" s="7">
-        <v>0</v>
-      </c>
       <c r="G50" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="H50" s="7" t="s">
         <v>101</v>
       </c>
+      <c r="H50" s="7">
+        <v>3</v>
+      </c>
       <c r="I50" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J50" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K50" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L50" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M50" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N50" s="7">
-        <v>3</v>
-      </c>
-      <c r="O50" s="7">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:14">
       <c r="A51" s="7">
         <v>2</v>
       </c>
@@ -8498,22 +8345,22 @@
         <v>51</v>
       </c>
       <c r="E51" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="F51" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="F51" s="7">
-        <v>0</v>
-      </c>
       <c r="G51" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="H51" s="7" t="s">
         <v>101</v>
       </c>
+      <c r="H51" s="7">
+        <v>4</v>
+      </c>
       <c r="I51" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J51" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K51" s="7">
         <v>5</v>
@@ -8522,16 +8369,13 @@
         <v>5</v>
       </c>
       <c r="M51" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N51" s="7">
-        <v>3</v>
-      </c>
-      <c r="O51" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:14">
       <c r="A52" s="7">
         <v>3</v>
       </c>
@@ -8545,40 +8389,37 @@
         <v>51</v>
       </c>
       <c r="E52" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="F52" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="F52" s="7">
-        <v>0</v>
-      </c>
       <c r="G52" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="H52" s="7" t="s">
         <v>101</v>
       </c>
+      <c r="H52" s="7">
+        <v>4</v>
+      </c>
       <c r="I52" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J52" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K52" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L52" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M52" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N52" s="7">
-        <v>3</v>
-      </c>
-      <c r="O52" s="7">
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="1:14">
       <c r="A53" s="7">
         <v>1</v>
       </c>
@@ -8592,40 +8433,37 @@
         <v>51</v>
       </c>
       <c r="E53" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="F53" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="F53" s="7">
-        <v>0</v>
-      </c>
       <c r="G53" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="H53" s="7" t="s">
         <v>102</v>
       </c>
+      <c r="H53" s="7">
+        <v>4</v>
+      </c>
       <c r="I53" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J53" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K53" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L53" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M53" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N53" s="7">
-        <v>3</v>
-      </c>
-      <c r="O53" s="7">
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" spans="1:14">
       <c r="A54" s="7">
         <v>2</v>
       </c>
@@ -8639,40 +8477,37 @@
         <v>51</v>
       </c>
       <c r="E54" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="F54" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="F54" s="7">
-        <v>0</v>
-      </c>
       <c r="G54" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="H54" s="7" t="s">
         <v>102</v>
       </c>
+      <c r="H54" s="7">
+        <v>2</v>
+      </c>
       <c r="I54" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J54" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K54" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L54" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M54" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N54" s="7">
-        <v>2</v>
-      </c>
-      <c r="O54" s="7">
         <v>0.56666666666666665</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:14">
       <c r="A55" s="7">
         <v>3</v>
       </c>
@@ -8686,40 +8521,37 @@
         <v>51</v>
       </c>
       <c r="E55" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="F55" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="F55" s="7">
-        <v>0</v>
-      </c>
       <c r="G55" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="H55" s="7" t="s">
         <v>102</v>
       </c>
+      <c r="H55" s="7">
+        <v>5</v>
+      </c>
       <c r="I55" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J55" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K55" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L55" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M55" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N55" s="7">
-        <v>2</v>
-      </c>
-      <c r="O55" s="7">
         <v>0.73333333333333328</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:14">
       <c r="A56" s="7">
         <v>1</v>
       </c>
@@ -8735,38 +8567,35 @@
       <c r="E56" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F56" s="7">
-        <v>0</v>
+      <c r="F56" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H56" s="7" t="s">
         <v>62</v>
       </c>
+      <c r="H56" s="7">
+        <v>2</v>
+      </c>
       <c r="I56" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J56" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K56" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L56" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M56" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N56" s="7">
-        <v>2</v>
-      </c>
-      <c r="O56" s="7">
         <v>0.46666666666666667</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:14">
       <c r="A57" s="7">
         <v>2</v>
       </c>
@@ -8782,38 +8611,35 @@
       <c r="E57" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F57" s="7">
-        <v>0</v>
+      <c r="F57" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H57" s="7" t="s">
         <v>62</v>
       </c>
+      <c r="H57" s="7">
+        <v>2</v>
+      </c>
       <c r="I57" s="7">
         <v>2</v>
       </c>
       <c r="J57" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K57" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L57" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M57" s="7">
         <v>2</v>
       </c>
       <c r="N57" s="7">
-        <v>2</v>
-      </c>
-      <c r="O57" s="7">
         <v>0.56666666666666665</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:14">
       <c r="A58" s="7">
         <v>3</v>
       </c>
@@ -8829,38 +8655,35 @@
       <c r="E58" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F58" s="7">
-        <v>0</v>
+      <c r="F58" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H58" s="7" t="s">
         <v>62</v>
       </c>
+      <c r="H58" s="7">
+        <v>1</v>
+      </c>
       <c r="I58" s="7">
         <v>1</v>
       </c>
       <c r="J58" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K58" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L58" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M58" s="7">
         <v>1</v>
       </c>
       <c r="N58" s="7">
-        <v>1</v>
-      </c>
-      <c r="O58" s="7">
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:14">
       <c r="A59" s="7">
         <v>1</v>
       </c>
@@ -8874,40 +8697,37 @@
         <v>31</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="F59" s="7">
-        <v>0</v>
+        <v>351</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H59" s="7" t="s">
         <v>64</v>
       </c>
+      <c r="H59" s="7">
+        <v>4</v>
+      </c>
       <c r="I59" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J59" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K59" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L59" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M59" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N59" s="7">
-        <v>2</v>
-      </c>
-      <c r="O59" s="7">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:14">
       <c r="A60" s="7">
         <v>2</v>
       </c>
@@ -8921,22 +8741,22 @@
         <v>31</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="F60" s="7">
-        <v>0</v>
+        <v>351</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H60" s="7" t="s">
         <v>64</v>
       </c>
+      <c r="H60" s="7">
+        <v>4</v>
+      </c>
       <c r="I60" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J60" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K60" s="7">
         <v>5</v>
@@ -8945,16 +8765,13 @@
         <v>5</v>
       </c>
       <c r="M60" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N60" s="7">
-        <v>3</v>
-      </c>
-      <c r="O60" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:14">
       <c r="A61" s="7">
         <v>3</v>
       </c>
@@ -8968,40 +8785,37 @@
         <v>31</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="F61" s="7">
-        <v>0</v>
+        <v>351</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H61" s="7" t="s">
         <v>64</v>
       </c>
+      <c r="H61" s="7">
+        <v>3</v>
+      </c>
       <c r="I61" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J61" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K61" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L61" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M61" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N61" s="7">
-        <v>3</v>
-      </c>
-      <c r="O61" s="7">
         <v>0.73333333333333328</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:14">
       <c r="A62" s="7">
         <v>1</v>
       </c>
@@ -9015,22 +8829,22 @@
         <v>31</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="F62" s="7">
-        <v>0</v>
+        <v>352</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H62" s="7" t="s">
         <v>66</v>
       </c>
+      <c r="H62" s="7">
+        <v>3</v>
+      </c>
       <c r="I62" s="7">
         <v>3</v>
       </c>
       <c r="J62" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K62" s="7">
         <v>5</v>
@@ -9039,16 +8853,13 @@
         <v>5</v>
       </c>
       <c r="M62" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N62" s="7">
-        <v>3</v>
-      </c>
-      <c r="O62" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:14">
       <c r="A63" s="7">
         <v>2</v>
       </c>
@@ -9062,22 +8873,22 @@
         <v>31</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="F63" s="7">
-        <v>0</v>
+        <v>352</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H63" s="7" t="s">
         <v>66</v>
       </c>
+      <c r="H63" s="7">
+        <v>4</v>
+      </c>
       <c r="I63" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J63" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K63" s="7">
         <v>5</v>
@@ -9086,16 +8897,13 @@
         <v>5</v>
       </c>
       <c r="M63" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N63" s="7">
-        <v>3</v>
-      </c>
-      <c r="O63" s="7">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" spans="1:14">
       <c r="A64" s="7">
         <v>3</v>
       </c>
@@ -9109,22 +8917,22 @@
         <v>31</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="F64" s="7">
-        <v>0</v>
+        <v>352</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H64" s="7" t="s">
         <v>66</v>
       </c>
+      <c r="H64" s="7">
+        <v>3</v>
+      </c>
       <c r="I64" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J64" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K64" s="7">
         <v>5</v>
@@ -9133,16 +8941,13 @@
         <v>5</v>
       </c>
       <c r="M64" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N64" s="7">
-        <v>3</v>
-      </c>
-      <c r="O64" s="7">
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
+    <row r="65" spans="1:14">
       <c r="A65" s="7">
         <v>1</v>
       </c>
@@ -9156,40 +8961,37 @@
         <v>68</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="F65" s="7">
-        <v>0</v>
+        <v>353</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H65" s="7" t="s">
         <v>70</v>
       </c>
+      <c r="H65" s="7">
+        <v>5</v>
+      </c>
       <c r="I65" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J65" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K65" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L65" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M65" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N65" s="7">
-        <v>2</v>
-      </c>
-      <c r="O65" s="7">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:14">
       <c r="A66" s="7">
         <v>2</v>
       </c>
@@ -9203,40 +9005,37 @@
         <v>68</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="F66" s="7">
-        <v>0</v>
+        <v>353</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H66" s="7" t="s">
         <v>70</v>
       </c>
+      <c r="H66" s="7">
+        <v>4</v>
+      </c>
       <c r="I66" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J66" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K66" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L66" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M66" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N66" s="7">
-        <v>3</v>
-      </c>
-      <c r="O66" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="67" spans="1:15">
+    <row r="67" spans="1:14">
       <c r="A67" s="7">
         <v>3</v>
       </c>
@@ -9250,40 +9049,37 @@
         <v>68</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="F67" s="7">
-        <v>0</v>
+        <v>353</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H67" s="7" t="s">
         <v>70</v>
       </c>
+      <c r="H67" s="7">
+        <v>5</v>
+      </c>
       <c r="I67" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J67" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K67" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L67" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M67" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N67" s="7">
-        <v>2</v>
-      </c>
-      <c r="O67" s="7">
         <v>0.73333333333333328</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
+    <row r="68" spans="1:14">
       <c r="A68" s="7">
         <v>1</v>
       </c>
@@ -9299,20 +9095,20 @@
       <c r="E68" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F68" s="7">
-        <v>0</v>
+      <c r="F68" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H68" s="7" t="s">
         <v>74</v>
       </c>
+      <c r="H68" s="7">
+        <v>5</v>
+      </c>
       <c r="I68" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J68" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K68" s="7">
         <v>5</v>
@@ -9321,16 +9117,13 @@
         <v>5</v>
       </c>
       <c r="M68" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N68" s="7">
-        <v>2</v>
-      </c>
-      <c r="O68" s="7">
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:14">
       <c r="A69" s="7">
         <v>2</v>
       </c>
@@ -9346,38 +9139,35 @@
       <c r="E69" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F69" s="7">
-        <v>0</v>
+      <c r="F69" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H69" s="7" t="s">
         <v>74</v>
       </c>
+      <c r="H69" s="7">
+        <v>2</v>
+      </c>
       <c r="I69" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K69" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L69" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M69" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N69" s="7">
-        <v>2</v>
-      </c>
-      <c r="O69" s="7">
         <v>0.56666666666666665</v>
       </c>
     </row>
-    <row r="70" spans="1:15">
+    <row r="70" spans="1:14">
       <c r="A70" s="7">
         <v>3</v>
       </c>
@@ -9393,38 +9183,35 @@
       <c r="E70" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F70" s="7">
-        <v>0</v>
+      <c r="F70" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H70" s="7" t="s">
         <v>74</v>
       </c>
+      <c r="H70" s="7">
+        <v>5</v>
+      </c>
       <c r="I70" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J70" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K70" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L70" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M70" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N70" s="7">
-        <v>3</v>
-      </c>
-      <c r="O70" s="7">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="71" spans="1:15">
+    <row r="71" spans="1:14">
       <c r="A71" s="7">
         <v>1</v>
       </c>
@@ -9438,40 +9225,37 @@
         <v>68</v>
       </c>
       <c r="E71" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="F71" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="F71" s="7">
-        <v>0</v>
-      </c>
       <c r="G71" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="H71" s="7" t="s">
         <v>71</v>
       </c>
+      <c r="H71" s="7">
+        <v>4</v>
+      </c>
       <c r="I71" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J71" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K71" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L71" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M71" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N71" s="7">
-        <v>3</v>
-      </c>
-      <c r="O71" s="7">
         <v>0.7</v>
       </c>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="1:14">
       <c r="A72" s="7">
         <v>2</v>
       </c>
@@ -9485,40 +9269,37 @@
         <v>68</v>
       </c>
       <c r="E72" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="F72" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="F72" s="7">
-        <v>0</v>
-      </c>
       <c r="G72" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="H72" s="7" t="s">
         <v>71</v>
       </c>
+      <c r="H72" s="7">
+        <v>4</v>
+      </c>
       <c r="I72" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J72" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K72" s="7">
         <v>4</v>
       </c>
       <c r="L72" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M72" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N72" s="7">
-        <v>4</v>
-      </c>
-      <c r="O72" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:14">
       <c r="A73" s="7">
         <v>3</v>
       </c>
@@ -9532,40 +9313,37 @@
         <v>68</v>
       </c>
       <c r="E73" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="F73" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="F73" s="7">
-        <v>0</v>
-      </c>
       <c r="G73" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="H73" s="7" t="s">
         <v>71</v>
       </c>
+      <c r="H73" s="7">
+        <v>2</v>
+      </c>
       <c r="I73" s="7">
         <v>2</v>
       </c>
       <c r="J73" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K73" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L73" s="7">
         <v>3</v>
       </c>
       <c r="M73" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N73" s="7">
-        <v>2</v>
-      </c>
-      <c r="O73" s="7">
         <v>0.53333333333333333</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:14">
       <c r="A74" s="7">
         <v>1</v>
       </c>
@@ -9579,22 +9357,22 @@
         <v>51</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="F74" s="7">
-        <v>0</v>
+        <v>356</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H74" s="7" t="s">
         <v>53</v>
       </c>
+      <c r="H74" s="7">
+        <v>5</v>
+      </c>
       <c r="I74" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J74" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K74" s="7">
         <v>5</v>
@@ -9603,16 +9381,13 @@
         <v>5</v>
       </c>
       <c r="M74" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N74" s="7">
-        <v>3</v>
-      </c>
-      <c r="O74" s="7">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="75" spans="1:15">
+    <row r="75" spans="1:14">
       <c r="A75" s="7">
         <v>2</v>
       </c>
@@ -9626,22 +9401,22 @@
         <v>51</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="F75" s="7">
-        <v>0</v>
+        <v>356</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H75" s="7" t="s">
         <v>53</v>
       </c>
+      <c r="H75" s="7">
+        <v>4</v>
+      </c>
       <c r="I75" s="7">
         <v>4</v>
       </c>
       <c r="J75" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K75" s="7">
         <v>5</v>
@@ -9650,16 +9425,13 @@
         <v>5</v>
       </c>
       <c r="M75" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N75" s="7">
-        <v>4</v>
-      </c>
-      <c r="O75" s="7">
         <v>0.9</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:14">
       <c r="A76" s="7">
         <v>3</v>
       </c>
@@ -9673,40 +9445,37 @@
         <v>51</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="F76" s="7">
-        <v>0</v>
+        <v>356</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H76" s="7" t="s">
         <v>53</v>
       </c>
+      <c r="H76" s="7">
+        <v>4</v>
+      </c>
       <c r="I76" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J76" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K76" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L76" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M76" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N76" s="7">
-        <v>2</v>
-      </c>
-      <c r="O76" s="7">
         <v>0.7</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:14">
       <c r="A77" s="7">
         <v>1</v>
       </c>
@@ -9722,20 +9491,20 @@
       <c r="E77" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F77" s="7">
-        <v>0</v>
+      <c r="F77" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H77" s="7" t="s">
         <v>56</v>
       </c>
+      <c r="H77" s="7">
+        <v>3</v>
+      </c>
       <c r="I77" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J77" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K77" s="7">
         <v>5</v>
@@ -9744,16 +9513,13 @@
         <v>5</v>
       </c>
       <c r="M77" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N77" s="7">
-        <v>2</v>
-      </c>
-      <c r="O77" s="7">
         <v>0.73333333333333328</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:14">
       <c r="A78" s="7">
         <v>2</v>
       </c>
@@ -9769,38 +9535,35 @@
       <c r="E78" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F78" s="7">
-        <v>0</v>
+      <c r="F78" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H78" s="7" t="s">
         <v>56</v>
       </c>
+      <c r="H78" s="7">
+        <v>4</v>
+      </c>
       <c r="I78" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J78" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K78" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L78" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M78" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N78" s="7">
-        <v>4</v>
-      </c>
-      <c r="O78" s="7">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="79" spans="1:15">
+    <row r="79" spans="1:14">
       <c r="A79" s="7">
         <v>3</v>
       </c>
@@ -9816,38 +9579,35 @@
       <c r="E79" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F79" s="7">
-        <v>0</v>
+      <c r="F79" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H79" s="7" t="s">
         <v>56</v>
       </c>
+      <c r="H79" s="7">
+        <v>5</v>
+      </c>
       <c r="I79" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J79" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K79" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L79" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M79" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N79" s="7">
-        <v>2</v>
-      </c>
-      <c r="O79" s="7">
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:14">
       <c r="A80" s="7">
         <v>1</v>
       </c>
@@ -9861,17 +9621,17 @@
         <v>51</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="F80" s="7">
-        <v>0</v>
+        <v>357</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H80" s="7" t="s">
         <v>58</v>
       </c>
+      <c r="H80" s="7">
+        <v>5</v>
+      </c>
       <c r="I80" s="7">
         <v>5</v>
       </c>
@@ -9888,13 +9648,10 @@
         <v>5</v>
       </c>
       <c r="N80" s="7">
-        <v>5</v>
-      </c>
-      <c r="O80" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
       <c r="A81" s="7">
         <v>2</v>
       </c>
@@ -9908,22 +9665,22 @@
         <v>51</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="F81" s="7">
-        <v>0</v>
+        <v>357</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H81" s="7" t="s">
         <v>58</v>
       </c>
+      <c r="H81" s="7">
+        <v>5</v>
+      </c>
       <c r="I81" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J81" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K81" s="7">
         <v>5</v>
@@ -9935,13 +9692,10 @@
         <v>5</v>
       </c>
       <c r="N81" s="7">
-        <v>5</v>
-      </c>
-      <c r="O81" s="7">
         <v>0.96666666666666667</v>
       </c>
     </row>
-    <row r="82" spans="1:15">
+    <row r="82" spans="1:14">
       <c r="A82" s="7">
         <v>3</v>
       </c>
@@ -9955,22 +9709,22 @@
         <v>51</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="F82" s="7">
-        <v>0</v>
+        <v>357</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H82" s="7" t="s">
         <v>58</v>
       </c>
+      <c r="H82" s="7">
+        <v>5</v>
+      </c>
       <c r="I82" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J82" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K82" s="7">
         <v>5</v>
@@ -9982,13 +9736,10 @@
         <v>5</v>
       </c>
       <c r="N82" s="7">
-        <v>5</v>
-      </c>
-      <c r="O82" s="7">
         <v>0.96666666666666667</v>
       </c>
     </row>
-    <row r="83" spans="1:15">
+    <row r="83" spans="1:14">
       <c r="A83" s="7">
         <v>1</v>
       </c>
@@ -10002,40 +9753,37 @@
         <v>13</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="F83" s="7">
-        <v>0</v>
+        <v>358</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H83" s="7" t="s">
         <v>17</v>
       </c>
+      <c r="H83" s="7">
+        <v>5</v>
+      </c>
       <c r="I83" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J83" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K83" s="7">
         <v>4</v>
       </c>
       <c r="L83" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M83" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N83" s="7">
-        <v>3</v>
-      </c>
-      <c r="O83" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="84" spans="1:15">
+    <row r="84" spans="1:14">
       <c r="A84" s="7">
         <v>2</v>
       </c>
@@ -10049,22 +9797,22 @@
         <v>13</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="F84" s="7">
-        <v>0</v>
+        <v>358</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H84" s="7" t="s">
         <v>17</v>
       </c>
+      <c r="H84" s="7">
+        <v>4</v>
+      </c>
       <c r="I84" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J84" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K84" s="7">
         <v>5</v>
@@ -10073,16 +9821,13 @@
         <v>5</v>
       </c>
       <c r="M84" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N84" s="7">
-        <v>3</v>
-      </c>
-      <c r="O84" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="85" spans="1:15">
+    <row r="85" spans="1:14">
       <c r="A85" s="7">
         <v>3</v>
       </c>
@@ -10096,40 +9841,37 @@
         <v>13</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="F85" s="4">
-        <v>0</v>
+        <v>358</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H85" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="H85" s="7">
+        <v>4</v>
+      </c>
       <c r="I85" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J85" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K85" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L85" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M85" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N85" s="7">
-        <v>3</v>
-      </c>
-      <c r="O85" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="86" spans="1:15">
+    <row r="86" spans="1:14">
       <c r="A86" s="7">
         <v>1</v>
       </c>
@@ -10143,40 +9885,37 @@
         <v>13</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="F86" s="7">
-        <v>0</v>
+        <v>359</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H86" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="H86" s="7">
+        <v>4</v>
+      </c>
       <c r="I86" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J86" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K86" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L86" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M86" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N86" s="7">
-        <v>2</v>
-      </c>
-      <c r="O86" s="7">
         <v>0.6333333333333333</v>
       </c>
     </row>
-    <row r="87" spans="1:15">
+    <row r="87" spans="1:14">
       <c r="A87" s="7">
         <v>2</v>
       </c>
@@ -10190,40 +9929,37 @@
         <v>13</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="F87" s="7">
-        <v>0</v>
+        <v>359</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H87" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="H87" s="7">
+        <v>3</v>
+      </c>
       <c r="I87" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J87" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K87" s="7">
         <v>5</v>
       </c>
       <c r="L87" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M87" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N87" s="7">
-        <v>3</v>
-      </c>
-      <c r="O87" s="7">
         <v>0.73333333333333328</v>
       </c>
     </row>
-    <row r="88" spans="1:15">
+    <row r="88" spans="1:14">
       <c r="A88" s="7">
         <v>3</v>
       </c>
@@ -10237,40 +9973,37 @@
         <v>13</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="F88" s="7">
-        <v>0</v>
+        <v>359</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H88" s="7" t="s">
         <v>15</v>
       </c>
+      <c r="H88" s="7">
+        <v>3</v>
+      </c>
       <c r="I88" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J88" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K88" s="7">
         <v>4</v>
       </c>
       <c r="L88" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M88" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N88" s="7">
-        <v>3</v>
-      </c>
-      <c r="O88" s="7">
         <v>0.7</v>
       </c>
     </row>
-    <row r="89" spans="1:15">
+    <row r="89" spans="1:14">
       <c r="A89" s="7">
         <v>1</v>
       </c>
@@ -10284,40 +10017,37 @@
         <v>13</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="F89" s="7">
-        <v>0</v>
+        <v>360</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H89" s="7" t="s">
         <v>19</v>
       </c>
+      <c r="H89" s="7">
+        <v>1</v>
+      </c>
       <c r="I89" s="7">
         <v>1</v>
       </c>
       <c r="J89" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K89" s="7">
         <v>5</v>
       </c>
       <c r="L89" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M89" s="7">
         <v>1</v>
       </c>
       <c r="N89" s="7">
-        <v>1</v>
-      </c>
-      <c r="O89" s="7">
         <v>0.46666666666666667</v>
       </c>
     </row>
-    <row r="90" spans="1:15">
+    <row r="90" spans="1:14">
       <c r="A90" s="7">
         <v>2</v>
       </c>
@@ -10331,40 +10061,37 @@
         <v>13</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="F90" s="7">
-        <v>0</v>
+        <v>360</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H90" s="7" t="s">
         <v>19</v>
       </c>
+      <c r="H90" s="7">
+        <v>3</v>
+      </c>
       <c r="I90" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J90" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K90" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L90" s="7">
         <v>4</v>
       </c>
       <c r="M90" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N90" s="7">
-        <v>3</v>
-      </c>
-      <c r="O90" s="7">
         <v>0.7</v>
       </c>
     </row>
-    <row r="91" spans="1:15">
+    <row r="91" spans="1:14">
       <c r="A91" s="7">
         <v>3</v>
       </c>
@@ -10378,40 +10105,37 @@
         <v>13</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="F91" s="7">
-        <v>0</v>
+        <v>360</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H91" s="7" t="s">
         <v>19</v>
       </c>
+      <c r="H91" s="7">
+        <v>3</v>
+      </c>
       <c r="I91" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J91" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K91" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L91" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M91" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N91" s="7">
-        <v>2</v>
-      </c>
-      <c r="O91" s="7">
         <v>0.6</v>
       </c>
     </row>
-    <row r="92" spans="1:15">
+    <row r="92" spans="1:14">
       <c r="A92" s="7">
         <v>1</v>
       </c>
@@ -10425,40 +10149,37 @@
         <v>43</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="F92" s="7">
-        <v>0</v>
+        <v>361</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H92" s="7" t="s">
         <v>45</v>
       </c>
+      <c r="H92" s="7">
+        <v>5</v>
+      </c>
       <c r="I92" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J92" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K92" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L92" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M92" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N92" s="7">
-        <v>3</v>
-      </c>
-      <c r="O92" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="93" spans="1:15">
+    <row r="93" spans="1:14">
       <c r="A93" s="7">
         <v>2</v>
       </c>
@@ -10472,22 +10193,22 @@
         <v>43</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="F93" s="7">
-        <v>0</v>
+        <v>361</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H93" s="7" t="s">
         <v>45</v>
       </c>
+      <c r="H93" s="7">
+        <v>4</v>
+      </c>
       <c r="I93" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J93" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K93" s="7">
         <v>5</v>
@@ -10496,16 +10217,13 @@
         <v>5</v>
       </c>
       <c r="M93" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N93" s="7">
-        <v>4</v>
-      </c>
-      <c r="O93" s="7">
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="94" spans="1:15">
+    <row r="94" spans="1:14">
       <c r="A94" s="7">
         <v>3</v>
       </c>
@@ -10519,40 +10237,37 @@
         <v>43</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="F94" s="7">
-        <v>0</v>
+        <v>361</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H94" s="7" t="s">
         <v>45</v>
       </c>
+      <c r="H94" s="7">
+        <v>5</v>
+      </c>
       <c r="I94" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J94" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K94" s="7">
         <v>4</v>
       </c>
       <c r="L94" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M94" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N94" s="7">
-        <v>3</v>
-      </c>
-      <c r="O94" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="95" spans="1:15">
+    <row r="95" spans="1:14">
       <c r="A95" s="7">
         <v>1</v>
       </c>
@@ -10566,22 +10281,22 @@
         <v>43</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="F95" s="7">
-        <v>0</v>
+        <v>362</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H95" s="7" t="s">
         <v>49</v>
       </c>
+      <c r="H95" s="7">
+        <v>5</v>
+      </c>
       <c r="I95" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J95" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K95" s="7">
         <v>5</v>
@@ -10590,16 +10305,13 @@
         <v>5</v>
       </c>
       <c r="M95" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N95" s="7">
-        <v>4</v>
-      </c>
-      <c r="O95" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="96" spans="1:15">
+    <row r="96" spans="1:14">
       <c r="A96" s="7">
         <v>2</v>
       </c>
@@ -10613,22 +10325,22 @@
         <v>43</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="F96" s="7">
-        <v>0</v>
+        <v>362</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H96" s="7" t="s">
         <v>49</v>
       </c>
+      <c r="H96" s="7">
+        <v>5</v>
+      </c>
       <c r="I96" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J96" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K96" s="7">
         <v>5</v>
@@ -10637,16 +10349,13 @@
         <v>5</v>
       </c>
       <c r="M96" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N96" s="7">
-        <v>4</v>
-      </c>
-      <c r="O96" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="97" spans="1:15">
+    <row r="97" spans="1:14">
       <c r="A97" s="7">
         <v>3</v>
       </c>
@@ -10660,40 +10369,37 @@
         <v>43</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="F97" s="7">
-        <v>0</v>
+        <v>362</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H97" s="7" t="s">
         <v>49</v>
       </c>
+      <c r="H97" s="7">
+        <v>5</v>
+      </c>
       <c r="I97" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J97" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K97" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L97" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M97" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N97" s="7">
-        <v>4</v>
-      </c>
-      <c r="O97" s="7">
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="98" spans="1:15">
+    <row r="98" spans="1:14">
       <c r="A98" s="7">
         <v>1</v>
       </c>
@@ -10707,40 +10413,37 @@
         <v>43</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="F98" s="7">
-        <v>0</v>
+        <v>363</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H98" s="7" t="s">
         <v>47</v>
       </c>
+      <c r="H98" s="7">
+        <v>3</v>
+      </c>
       <c r="I98" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J98" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K98" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L98" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M98" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N98" s="7">
-        <v>3</v>
-      </c>
-      <c r="O98" s="7">
         <v>0.7</v>
       </c>
     </row>
-    <row r="99" spans="1:15">
+    <row r="99" spans="1:14">
       <c r="A99" s="7">
         <v>2</v>
       </c>
@@ -10754,22 +10457,22 @@
         <v>43</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="F99" s="7">
-        <v>0</v>
+        <v>363</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H99" s="7" t="s">
         <v>47</v>
       </c>
+      <c r="H99" s="7">
+        <v>4</v>
+      </c>
       <c r="I99" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J99" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K99" s="7">
         <v>5</v>
@@ -10778,16 +10481,13 @@
         <v>5</v>
       </c>
       <c r="M99" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N99" s="7">
-        <v>3</v>
-      </c>
-      <c r="O99" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="100" spans="1:15">
+    <row r="100" spans="1:14">
       <c r="A100" s="7">
         <v>3</v>
       </c>
@@ -10801,40 +10501,37 @@
         <v>43</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="F100" s="7">
-        <v>0</v>
+        <v>363</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H100" s="7" t="s">
         <v>47</v>
       </c>
+      <c r="H100" s="7">
+        <v>3</v>
+      </c>
       <c r="I100" s="7">
         <v>3</v>
       </c>
       <c r="J100" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K100" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L100" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M100" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N100" s="7">
-        <v>3</v>
-      </c>
-      <c r="O100" s="7">
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="101" spans="1:15">
+    <row r="101" spans="1:14">
       <c r="A101" s="7">
         <v>1</v>
       </c>
@@ -10848,40 +10545,37 @@
         <v>115</v>
       </c>
       <c r="E101" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="F101" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="F101" s="7">
-        <v>0</v>
-      </c>
       <c r="G101" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="H101" s="7" t="s">
         <v>119</v>
       </c>
+      <c r="H101" s="7">
+        <v>3</v>
+      </c>
       <c r="I101" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J101" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K101" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L101" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M101" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N101" s="7">
-        <v>2</v>
-      </c>
-      <c r="O101" s="7">
         <v>0.6333333333333333</v>
       </c>
     </row>
-    <row r="102" spans="1:15">
+    <row r="102" spans="1:14">
       <c r="A102" s="7">
         <v>2</v>
       </c>
@@ -10895,22 +10589,22 @@
         <v>115</v>
       </c>
       <c r="E102" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="F102" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="F102" s="7">
-        <v>0</v>
-      </c>
       <c r="G102" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="H102" s="7" t="s">
         <v>119</v>
       </c>
+      <c r="H102" s="7">
+        <v>5</v>
+      </c>
       <c r="I102" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J102" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K102" s="7">
         <v>5</v>
@@ -10919,16 +10613,13 @@
         <v>5</v>
       </c>
       <c r="M102" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N102" s="7">
-        <v>2</v>
-      </c>
-      <c r="O102" s="7">
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="103" spans="1:15">
+    <row r="103" spans="1:14">
       <c r="A103" s="7">
         <v>3</v>
       </c>
@@ -10942,40 +10633,37 @@
         <v>115</v>
       </c>
       <c r="E103" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="F103" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="F103" s="7">
-        <v>0</v>
-      </c>
       <c r="G103" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="H103" s="7" t="s">
         <v>119</v>
       </c>
+      <c r="H103" s="7">
+        <v>4</v>
+      </c>
       <c r="I103" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J103" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K103" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L103" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M103" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N103" s="7">
-        <v>2</v>
-      </c>
-      <c r="O103" s="7">
         <v>0.7</v>
       </c>
     </row>
-    <row r="104" spans="1:15">
+    <row r="104" spans="1:14">
       <c r="A104" s="7">
         <v>1</v>
       </c>
@@ -10989,17 +10677,17 @@
         <v>115</v>
       </c>
       <c r="E104" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="F104" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="F104" s="7">
-        <v>0</v>
-      </c>
       <c r="G104" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="H104" s="7" t="s">
         <v>116</v>
       </c>
+      <c r="H104" s="7">
+        <v>5</v>
+      </c>
       <c r="I104" s="7">
         <v>5</v>
       </c>
@@ -11007,22 +10695,19 @@
         <v>5</v>
       </c>
       <c r="K104" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L104" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M104" s="7">
         <v>5</v>
       </c>
       <c r="N104" s="7">
-        <v>5</v>
-      </c>
-      <c r="O104" s="7">
         <v>0.96666666666666667</v>
       </c>
     </row>
-    <row r="105" spans="1:15">
+    <row r="105" spans="1:14">
       <c r="A105" s="7">
         <v>2</v>
       </c>
@@ -11036,22 +10721,22 @@
         <v>115</v>
       </c>
       <c r="E105" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="F105" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="F105" s="7">
-        <v>0</v>
-      </c>
       <c r="G105" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="H105" s="7" t="s">
         <v>116</v>
       </c>
+      <c r="H105" s="7">
+        <v>5</v>
+      </c>
       <c r="I105" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J105" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K105" s="7">
         <v>5</v>
@@ -11060,16 +10745,13 @@
         <v>5</v>
       </c>
       <c r="M105" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N105" s="7">
-        <v>4</v>
-      </c>
-      <c r="O105" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="106" spans="1:15">
+    <row r="106" spans="1:14">
       <c r="A106" s="7">
         <v>3</v>
       </c>
@@ -11083,22 +10765,22 @@
         <v>115</v>
       </c>
       <c r="E106" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="F106" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="F106" s="7">
-        <v>0</v>
-      </c>
       <c r="G106" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="H106" s="7" t="s">
         <v>116</v>
       </c>
+      <c r="H106" s="7">
+        <v>5</v>
+      </c>
       <c r="I106" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J106" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K106" s="7">
         <v>5</v>
@@ -11107,16 +10789,13 @@
         <v>5</v>
       </c>
       <c r="M106" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N106" s="7">
-        <v>4</v>
-      </c>
-      <c r="O106" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="107" spans="1:15">
+    <row r="107" spans="1:14">
       <c r="A107" s="7">
         <v>1</v>
       </c>
@@ -11130,40 +10809,37 @@
         <v>115</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="F107" s="7">
-        <v>0</v>
+        <v>368</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="H107" s="7" t="s">
         <v>118</v>
       </c>
+      <c r="H107" s="7">
+        <v>2</v>
+      </c>
       <c r="I107" s="7">
         <v>2</v>
       </c>
       <c r="J107" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K107" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L107" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M107" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N107" s="7">
-        <v>3</v>
-      </c>
-      <c r="O107" s="7">
         <v>0.7</v>
       </c>
     </row>
-    <row r="108" spans="1:15">
+    <row r="108" spans="1:14">
       <c r="A108" s="7">
         <v>2</v>
       </c>
@@ -11177,22 +10853,22 @@
         <v>115</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="F108" s="7">
-        <v>0</v>
+        <v>368</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="H108" s="7" t="s">
         <v>118</v>
       </c>
+      <c r="H108" s="7">
+        <v>4</v>
+      </c>
       <c r="I108" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J108" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K108" s="7">
         <v>5</v>
@@ -11201,16 +10877,13 @@
         <v>5</v>
       </c>
       <c r="M108" s="7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N108" s="7">
-        <v>2</v>
-      </c>
-      <c r="O108" s="7">
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="109" spans="1:15">
+    <row r="109" spans="1:14">
       <c r="A109" s="7">
         <v>3</v>
       </c>
@@ -11224,40 +10897,37 @@
         <v>115</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="F109" s="7">
-        <v>0</v>
+        <v>368</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="H109" s="7" t="s">
         <v>118</v>
       </c>
+      <c r="H109" s="7">
+        <v>3</v>
+      </c>
       <c r="I109" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J109" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K109" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L109" s="7">
         <v>4</v>
       </c>
       <c r="M109" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N109" s="7">
-        <v>3</v>
-      </c>
-      <c r="O109" s="7">
         <v>0.7</v>
       </c>
     </row>
-    <row r="110" spans="1:15">
+    <row r="110" spans="1:14">
       <c r="A110" s="7">
         <v>1</v>
       </c>
@@ -11271,17 +10941,17 @@
         <v>31</v>
       </c>
       <c r="E110" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="F110" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="F110" s="7">
-        <v>0</v>
-      </c>
       <c r="G110" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="H110" s="7" t="s">
         <v>39</v>
       </c>
+      <c r="H110" s="7">
+        <v>5</v>
+      </c>
       <c r="I110" s="7">
         <v>5</v>
       </c>
@@ -11298,13 +10968,10 @@
         <v>5</v>
       </c>
       <c r="N110" s="7">
-        <v>5</v>
-      </c>
-      <c r="O110" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14">
       <c r="A111" s="7">
         <v>2</v>
       </c>
@@ -11318,22 +10985,22 @@
         <v>31</v>
       </c>
       <c r="E111" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="F111" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="F111" s="7">
-        <v>0</v>
-      </c>
       <c r="G111" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="H111" s="7" t="s">
         <v>39</v>
       </c>
+      <c r="H111" s="7">
+        <v>5</v>
+      </c>
       <c r="I111" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J111" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K111" s="7">
         <v>5</v>
@@ -11342,16 +11009,13 @@
         <v>5</v>
       </c>
       <c r="M111" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N111" s="7">
-        <v>4</v>
-      </c>
-      <c r="O111" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="112" spans="1:15">
+    <row r="112" spans="1:14">
       <c r="A112" s="7">
         <v>3</v>
       </c>
@@ -11365,22 +11029,22 @@
         <v>31</v>
       </c>
       <c r="E112" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="F112" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="F112" s="7">
-        <v>0</v>
-      </c>
       <c r="G112" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="H112" s="7" t="s">
         <v>39</v>
       </c>
+      <c r="H112" s="7">
+        <v>5</v>
+      </c>
       <c r="I112" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J112" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K112" s="7">
         <v>5</v>
@@ -11392,13 +11056,10 @@
         <v>5</v>
       </c>
       <c r="N112" s="7">
-        <v>5</v>
-      </c>
-      <c r="O112" s="7">
         <v>0.96666666666666667</v>
       </c>
     </row>
-    <row r="113" spans="1:15">
+    <row r="113" spans="1:14">
       <c r="A113" s="7">
         <v>1</v>
       </c>
@@ -11412,22 +11073,22 @@
         <v>31</v>
       </c>
       <c r="E113" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="F113" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="F113" s="7">
-        <v>0</v>
-      </c>
       <c r="G113" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="H113" s="7" t="s">
         <v>41</v>
       </c>
+      <c r="H113" s="7">
+        <v>3</v>
+      </c>
       <c r="I113" s="7">
         <v>3</v>
       </c>
       <c r="J113" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K113" s="7">
         <v>5</v>
@@ -11436,16 +11097,13 @@
         <v>5</v>
       </c>
       <c r="M113" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N113" s="7">
-        <v>3</v>
-      </c>
-      <c r="O113" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="114" spans="1:15">
+    <row r="114" spans="1:14">
       <c r="A114" s="7">
         <v>2</v>
       </c>
@@ -11459,40 +11117,37 @@
         <v>31</v>
       </c>
       <c r="E114" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="F114" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="F114" s="7">
-        <v>0</v>
-      </c>
       <c r="G114" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="H114" s="7" t="s">
         <v>41</v>
       </c>
+      <c r="H114" s="7">
+        <v>4</v>
+      </c>
       <c r="I114" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J114" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K114" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L114" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M114" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N114" s="7">
-        <v>4</v>
-      </c>
-      <c r="O114" s="7">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="115" spans="1:15">
+    <row r="115" spans="1:14">
       <c r="A115" s="7">
         <v>3</v>
       </c>
@@ -11506,40 +11161,37 @@
         <v>31</v>
       </c>
       <c r="E115" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="F115" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="F115" s="7">
-        <v>0</v>
-      </c>
       <c r="G115" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="H115" s="7" t="s">
         <v>41</v>
       </c>
+      <c r="H115" s="7">
+        <v>4</v>
+      </c>
       <c r="I115" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J115" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K115" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L115" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M115" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N115" s="7">
-        <v>3</v>
-      </c>
-      <c r="O115" s="7">
         <v>0.8</v>
       </c>
     </row>
-    <row r="116" spans="1:15">
+    <row r="116" spans="1:14">
       <c r="A116" s="7">
         <v>1</v>
       </c>
@@ -11553,40 +11205,37 @@
         <v>31</v>
       </c>
       <c r="E116" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="F116" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="F116" s="7">
-        <v>0</v>
-      </c>
       <c r="G116" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="H116" s="7" t="s">
         <v>40</v>
       </c>
+      <c r="H116" s="7">
+        <v>4</v>
+      </c>
       <c r="I116" s="7">
         <v>4</v>
       </c>
       <c r="J116" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K116" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L116" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M116" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N116" s="7">
-        <v>4</v>
-      </c>
-      <c r="O116" s="7">
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="117" spans="1:15">
+    <row r="117" spans="1:14">
       <c r="A117" s="7">
         <v>2</v>
       </c>
@@ -11600,22 +11249,22 @@
         <v>31</v>
       </c>
       <c r="E117" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="F117" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="F117" s="7">
-        <v>0</v>
-      </c>
       <c r="G117" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="H117" s="7" t="s">
         <v>40</v>
       </c>
+      <c r="H117" s="7">
+        <v>5</v>
+      </c>
       <c r="I117" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J117" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K117" s="7">
         <v>5</v>
@@ -11624,16 +11273,13 @@
         <v>5</v>
       </c>
       <c r="M117" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N117" s="7">
-        <v>4</v>
-      </c>
-      <c r="O117" s="7">
         <v>0.9</v>
       </c>
     </row>
-    <row r="118" spans="1:15">
+    <row r="118" spans="1:14">
       <c r="A118" s="7">
         <v>3</v>
       </c>
@@ -11647,40 +11293,37 @@
         <v>31</v>
       </c>
       <c r="E118" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="F118" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="F118" s="7">
-        <v>0</v>
-      </c>
       <c r="G118" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="H118" s="7" t="s">
         <v>40</v>
       </c>
+      <c r="H118" s="7">
+        <v>4</v>
+      </c>
       <c r="I118" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J118" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K118" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L118" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M118" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N118" s="7">
-        <v>4</v>
-      </c>
-      <c r="O118" s="7">
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="119" spans="1:15">
+    <row r="119" spans="1:14">
       <c r="A119" s="7">
         <v>1</v>
       </c>
@@ -11694,22 +11337,22 @@
         <v>31</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="F119" s="7">
-        <v>0</v>
+        <v>375</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H119" s="7" t="s">
         <v>37</v>
       </c>
+      <c r="H119" s="7">
+        <v>5</v>
+      </c>
       <c r="I119" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J119" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K119" s="7">
         <v>5</v>
@@ -11718,16 +11361,13 @@
         <v>5</v>
       </c>
       <c r="M119" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N119" s="7">
-        <v>4</v>
-      </c>
-      <c r="O119" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="120" spans="1:15">
+    <row r="120" spans="1:14">
       <c r="A120" s="7">
         <v>2</v>
       </c>
@@ -11741,40 +11381,37 @@
         <v>31</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="F120" s="7">
-        <v>0</v>
+        <v>375</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H120" s="7" t="s">
         <v>37</v>
       </c>
+      <c r="H120" s="7">
+        <v>4</v>
+      </c>
       <c r="I120" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J120" s="7">
         <v>5</v>
       </c>
       <c r="K120" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L120" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M120" s="7">
         <v>5</v>
       </c>
       <c r="N120" s="7">
-        <v>5</v>
-      </c>
-      <c r="O120" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="121" spans="1:15">
+    <row r="121" spans="1:14">
       <c r="A121" s="7">
         <v>3</v>
       </c>
@@ -11788,40 +11425,37 @@
         <v>31</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="F121" s="7">
-        <v>0</v>
+        <v>375</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H121" s="7" t="s">
         <v>37</v>
       </c>
+      <c r="H121" s="7">
+        <v>4</v>
+      </c>
       <c r="I121" s="7">
         <v>4</v>
       </c>
       <c r="J121" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K121" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L121" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M121" s="7">
         <v>5</v>
       </c>
       <c r="N121" s="7">
-        <v>5</v>
-      </c>
-      <c r="O121" s="7">
         <v>0.9</v>
       </c>
     </row>
-    <row r="122" spans="1:15">
+    <row r="122" spans="1:14">
       <c r="A122" s="7">
         <v>1</v>
       </c>
@@ -11835,22 +11469,22 @@
         <v>31</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="F122" s="7">
-        <v>0</v>
+        <v>376</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H122" s="7" t="s">
         <v>33</v>
       </c>
+      <c r="H122" s="7">
+        <v>5</v>
+      </c>
       <c r="I122" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J122" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K122" s="7">
         <v>5</v>
@@ -11859,16 +11493,13 @@
         <v>5</v>
       </c>
       <c r="M122" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N122" s="7">
-        <v>4</v>
-      </c>
-      <c r="O122" s="7">
         <v>0.9</v>
       </c>
     </row>
-    <row r="123" spans="1:15">
+    <row r="123" spans="1:14">
       <c r="A123" s="7">
         <v>2</v>
       </c>
@@ -11882,22 +11513,22 @@
         <v>31</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="F123" s="7">
-        <v>0</v>
+        <v>376</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H123" s="7" t="s">
         <v>33</v>
       </c>
+      <c r="H123" s="7">
+        <v>4</v>
+      </c>
       <c r="I123" s="7">
         <v>4</v>
       </c>
       <c r="J123" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K123" s="7">
         <v>5</v>
@@ -11906,16 +11537,13 @@
         <v>5</v>
       </c>
       <c r="M123" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N123" s="7">
-        <v>4</v>
-      </c>
-      <c r="O123" s="7">
         <v>0.9</v>
       </c>
     </row>
-    <row r="124" spans="1:15">
+    <row r="124" spans="1:14">
       <c r="A124" s="7">
         <v>3</v>
       </c>
@@ -11929,22 +11557,22 @@
         <v>31</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="F124" s="7">
-        <v>0</v>
+        <v>376</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H124" s="7" t="s">
         <v>33</v>
       </c>
+      <c r="H124" s="7">
+        <v>5</v>
+      </c>
       <c r="I124" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J124" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K124" s="7">
         <v>5</v>
@@ -11953,16 +11581,13 @@
         <v>5</v>
       </c>
       <c r="M124" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N124" s="7">
-        <v>4</v>
-      </c>
-      <c r="O124" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="125" spans="1:15">
+    <row r="125" spans="1:14">
       <c r="A125" s="7">
         <v>1</v>
       </c>
@@ -11976,40 +11601,37 @@
         <v>31</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="F125" s="7">
-        <v>0</v>
+        <v>377</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H125" s="7" t="s">
         <v>35</v>
       </c>
+      <c r="H125" s="7">
+        <v>5</v>
+      </c>
       <c r="I125" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J125" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K125" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L125" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M125" s="7">
         <v>5</v>
       </c>
       <c r="N125" s="7">
-        <v>5</v>
-      </c>
-      <c r="O125" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="126" spans="1:15">
+    <row r="126" spans="1:14">
       <c r="A126" s="7">
         <v>2</v>
       </c>
@@ -12023,22 +11645,22 @@
         <v>31</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="F126" s="7">
-        <v>0</v>
+        <v>377</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="G126" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H126" s="7" t="s">
         <v>35</v>
       </c>
+      <c r="H126" s="7">
+        <v>5</v>
+      </c>
       <c r="I126" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J126" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K126" s="7">
         <v>5</v>
@@ -12047,16 +11669,13 @@
         <v>5</v>
       </c>
       <c r="M126" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N126" s="7">
-        <v>4</v>
-      </c>
-      <c r="O126" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="127" spans="1:15">
+    <row r="127" spans="1:14">
       <c r="A127" s="7">
         <v>3</v>
       </c>
@@ -12070,22 +11689,22 @@
         <v>31</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="F127" s="7">
-        <v>0</v>
+        <v>377</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="G127" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H127" s="7" t="s">
         <v>35</v>
       </c>
+      <c r="H127" s="7">
+        <v>5</v>
+      </c>
       <c r="I127" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J127" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K127" s="7">
         <v>5</v>
@@ -12097,13 +11716,10 @@
         <v>5</v>
       </c>
       <c r="N127" s="7">
-        <v>5</v>
-      </c>
-      <c r="O127" s="7">
         <v>0.96666666666666667</v>
       </c>
     </row>
-    <row r="128" spans="1:15">
+    <row r="128" spans="1:14">
       <c r="A128" s="7">
         <v>1</v>
       </c>
@@ -12117,22 +11733,22 @@
         <v>13</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="F128" s="7">
-        <v>0</v>
+        <v>378</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="G128" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H128" s="7" t="s">
         <v>23</v>
       </c>
+      <c r="H128" s="7">
+        <v>4</v>
+      </c>
       <c r="I128" s="7">
         <v>4</v>
       </c>
       <c r="J128" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K128" s="7">
         <v>5</v>
@@ -12141,16 +11757,13 @@
         <v>5</v>
       </c>
       <c r="M128" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N128" s="7">
-        <v>4</v>
-      </c>
-      <c r="O128" s="7">
         <v>0.9</v>
       </c>
     </row>
-    <row r="129" spans="1:15">
+    <row r="129" spans="1:14">
       <c r="A129" s="7">
         <v>2</v>
       </c>
@@ -12164,22 +11777,22 @@
         <v>13</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="F129" s="7">
-        <v>0</v>
+        <v>378</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="G129" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H129" s="7" t="s">
         <v>23</v>
       </c>
+      <c r="H129" s="7">
+        <v>5</v>
+      </c>
       <c r="I129" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J129" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K129" s="7">
         <v>5</v>
@@ -12188,16 +11801,13 @@
         <v>5</v>
       </c>
       <c r="M129" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N129" s="7">
-        <v>4</v>
-      </c>
-      <c r="O129" s="7">
         <v>0.9</v>
       </c>
     </row>
-    <row r="130" spans="1:15">
+    <row r="130" spans="1:14">
       <c r="A130" s="7">
         <v>3</v>
       </c>
@@ -12211,40 +11821,37 @@
         <v>13</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="F130" s="7">
-        <v>0</v>
+        <v>378</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="G130" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H130" s="7" t="s">
         <v>23</v>
       </c>
+      <c r="H130" s="7">
+        <v>4</v>
+      </c>
       <c r="I130" s="7">
         <v>4</v>
       </c>
       <c r="J130" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K130" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L130" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M130" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N130" s="7">
-        <v>4</v>
-      </c>
-      <c r="O130" s="7">
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="131" spans="1:15">
+    <row r="131" spans="1:14">
       <c r="A131" s="7">
         <v>1</v>
       </c>
@@ -12258,40 +11865,37 @@
         <v>13</v>
       </c>
       <c r="E131" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="F131" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="F131" s="7">
-        <v>0</v>
-      </c>
       <c r="G131" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="H131" s="7" t="s">
         <v>21</v>
       </c>
+      <c r="H131" s="7">
+        <v>5</v>
+      </c>
       <c r="I131" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J131" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K131" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L131" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M131" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N131" s="7">
-        <v>1</v>
-      </c>
-      <c r="O131" s="7">
         <v>0.6</v>
       </c>
     </row>
-    <row r="132" spans="1:15">
+    <row r="132" spans="1:14">
       <c r="A132" s="7">
         <v>2</v>
       </c>
@@ -12305,40 +11909,37 @@
         <v>13</v>
       </c>
       <c r="E132" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="F132" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="F132" s="7">
-        <v>0</v>
-      </c>
       <c r="G132" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="H132" s="7" t="s">
         <v>21</v>
       </c>
+      <c r="H132" s="7">
+        <v>4</v>
+      </c>
       <c r="I132" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J132" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K132" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L132" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M132" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N132" s="7">
-        <v>3</v>
-      </c>
-      <c r="O132" s="7">
         <v>0.76666666666666672</v>
       </c>
     </row>
-    <row r="133" spans="1:15">
+    <row r="133" spans="1:14">
       <c r="A133" s="7">
         <v>3</v>
       </c>
@@ -12352,22 +11953,22 @@
         <v>13</v>
       </c>
       <c r="E133" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="F133" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="F133" s="7">
-        <v>0</v>
-      </c>
       <c r="G133" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="H133" s="7" t="s">
         <v>21</v>
       </c>
+      <c r="H133" s="7">
+        <v>2</v>
+      </c>
       <c r="I133" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J133" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K133" s="7">
         <v>4</v>
@@ -12376,16 +11977,13 @@
         <v>4</v>
       </c>
       <c r="M133" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N133" s="7">
-        <v>3</v>
-      </c>
-      <c r="O133" s="7">
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="134" spans="1:15">
+    <row r="134" spans="1:14">
       <c r="A134" s="7">
         <v>1</v>
       </c>
@@ -12399,22 +11997,22 @@
         <v>13</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="F134" s="7">
-        <v>0</v>
+        <v>381</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="G134" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H134" s="7" t="s">
         <v>25</v>
       </c>
+      <c r="H134" s="7">
+        <v>5</v>
+      </c>
       <c r="I134" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J134" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K134" s="7">
         <v>5</v>
@@ -12426,13 +12024,10 @@
         <v>5</v>
       </c>
       <c r="N134" s="7">
-        <v>5</v>
-      </c>
-      <c r="O134" s="7">
         <v>0.96666666666666667</v>
       </c>
     </row>
-    <row r="135" spans="1:15">
+    <row r="135" spans="1:14">
       <c r="A135" s="7">
         <v>2</v>
       </c>
@@ -12446,22 +12041,22 @@
         <v>13</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="F135" s="7">
-        <v>0</v>
+        <v>381</v>
+      </c>
+      <c r="F135" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="G135" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H135" s="7" t="s">
         <v>25</v>
       </c>
+      <c r="H135" s="7">
+        <v>5</v>
+      </c>
       <c r="I135" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J135" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K135" s="7">
         <v>5</v>
@@ -12470,16 +12065,13 @@
         <v>5</v>
       </c>
       <c r="M135" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N135" s="7">
-        <v>4</v>
-      </c>
-      <c r="O135" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="136" spans="1:15">
+    <row r="136" spans="1:14">
       <c r="A136" s="7">
         <v>3</v>
       </c>
@@ -12493,22 +12085,22 @@
         <v>13</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="F136" s="7">
-        <v>0</v>
+        <v>381</v>
+      </c>
+      <c r="F136" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="G136" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H136" s="7" t="s">
         <v>25</v>
       </c>
+      <c r="H136" s="7">
+        <v>5</v>
+      </c>
       <c r="I136" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J136" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K136" s="7">
         <v>5</v>
@@ -12517,16 +12109,13 @@
         <v>5</v>
       </c>
       <c r="M136" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N136" s="7">
-        <v>4</v>
-      </c>
-      <c r="O136" s="7">
         <v>0.9</v>
       </c>
     </row>
-    <row r="137" spans="1:15">
+    <row r="137" spans="1:14">
       <c r="A137" s="7">
         <v>1</v>
       </c>
@@ -12540,22 +12129,22 @@
         <v>13</v>
       </c>
       <c r="E137" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="F137" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="F137" s="7">
-        <v>0</v>
-      </c>
       <c r="G137" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="H137" s="7" t="s">
         <v>27</v>
       </c>
+      <c r="H137" s="7">
+        <v>5</v>
+      </c>
       <c r="I137" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J137" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K137" s="7">
         <v>5</v>
@@ -12564,16 +12153,13 @@
         <v>5</v>
       </c>
       <c r="M137" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N137" s="7">
-        <v>4</v>
-      </c>
-      <c r="O137" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="138" spans="1:15">
+    <row r="138" spans="1:14">
       <c r="A138" s="7">
         <v>2</v>
       </c>
@@ -12587,22 +12173,22 @@
         <v>13</v>
       </c>
       <c r="E138" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="F138" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="F138" s="7">
-        <v>0</v>
-      </c>
       <c r="G138" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="H138" s="7" t="s">
         <v>27</v>
       </c>
+      <c r="H138" s="7">
+        <v>4</v>
+      </c>
       <c r="I138" s="7">
         <v>4</v>
       </c>
       <c r="J138" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K138" s="7">
         <v>5</v>
@@ -12611,16 +12197,13 @@
         <v>5</v>
       </c>
       <c r="M138" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N138" s="7">
-        <v>4</v>
-      </c>
-      <c r="O138" s="7">
         <v>0.9</v>
       </c>
     </row>
-    <row r="139" spans="1:15">
+    <row r="139" spans="1:14">
       <c r="A139" s="7">
         <v>3</v>
       </c>
@@ -12634,40 +12217,37 @@
         <v>13</v>
       </c>
       <c r="E139" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="F139" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="F139" s="7">
-        <v>0</v>
-      </c>
       <c r="G139" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="H139" s="7" t="s">
         <v>27</v>
       </c>
+      <c r="H139" s="7">
+        <v>5</v>
+      </c>
       <c r="I139" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J139" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K139" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L139" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M139" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N139" s="7">
-        <v>4</v>
-      </c>
-      <c r="O139" s="7">
         <v>0.8666666666666667</v>
       </c>
     </row>
-    <row r="140" spans="1:15">
+    <row r="140" spans="1:14">
       <c r="A140" s="7">
         <v>1</v>
       </c>
@@ -12681,40 +12261,37 @@
         <v>13</v>
       </c>
       <c r="E140" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F140" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="F140" s="7">
-        <v>0</v>
-      </c>
       <c r="G140" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="H140" s="7" t="s">
         <v>29</v>
       </c>
+      <c r="H140" s="7">
+        <v>2</v>
+      </c>
       <c r="I140" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J140" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K140" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L140" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M140" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N140" s="7">
-        <v>2</v>
-      </c>
-      <c r="O140" s="7">
         <v>0.5</v>
       </c>
     </row>
-    <row r="141" spans="1:15">
+    <row r="141" spans="1:14">
       <c r="A141" s="7">
         <v>2</v>
       </c>
@@ -12728,40 +12305,37 @@
         <v>13</v>
       </c>
       <c r="E141" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F141" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="F141" s="7">
-        <v>0</v>
-      </c>
       <c r="G141" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="H141" s="7" t="s">
         <v>29</v>
       </c>
+      <c r="H141" s="7">
+        <v>3</v>
+      </c>
       <c r="I141" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J141" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K141" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L141" s="7">
         <v>4</v>
       </c>
       <c r="M141" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N141" s="7">
-        <v>3</v>
-      </c>
-      <c r="O141" s="7">
         <v>0.7</v>
       </c>
     </row>
-    <row r="142" spans="1:15">
+    <row r="142" spans="1:14">
       <c r="A142" s="7">
         <v>3</v>
       </c>
@@ -12775,40 +12349,37 @@
         <v>13</v>
       </c>
       <c r="E142" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F142" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="F142" s="7">
-        <v>0</v>
-      </c>
       <c r="G142" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="H142" s="7" t="s">
         <v>29</v>
       </c>
+      <c r="H142" s="7">
+        <v>1</v>
+      </c>
       <c r="I142" s="7">
         <v>1</v>
       </c>
       <c r="J142" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K142" s="7">
         <v>5</v>
       </c>
       <c r="L142" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M142" s="7">
         <v>1</v>
       </c>
       <c r="N142" s="7">
-        <v>1</v>
-      </c>
-      <c r="O142" s="7">
         <v>0.46666666666666667</v>
       </c>
     </row>
-    <row r="143" spans="1:15">
+    <row r="143" spans="1:14">
       <c r="A143" s="7">
         <v>1</v>
       </c>
@@ -12822,22 +12393,22 @@
         <v>13</v>
       </c>
       <c r="E143" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="F143" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="F143" s="7">
-        <v>0</v>
-      </c>
       <c r="G143" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="H143" s="7" t="s">
         <v>28</v>
       </c>
+      <c r="H143" s="7">
+        <v>5</v>
+      </c>
       <c r="I143" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J143" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K143" s="7">
         <v>5</v>
@@ -12846,16 +12417,13 @@
         <v>5</v>
       </c>
       <c r="M143" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N143" s="7">
-        <v>4</v>
-      </c>
-      <c r="O143" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="144" spans="1:15">
+    <row r="144" spans="1:14">
       <c r="A144" s="7">
         <v>2</v>
       </c>
@@ -12869,22 +12437,22 @@
         <v>13</v>
       </c>
       <c r="E144" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="F144" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="F144" s="7">
-        <v>0</v>
-      </c>
       <c r="G144" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="H144" s="7" t="s">
         <v>28</v>
       </c>
+      <c r="H144" s="7">
+        <v>5</v>
+      </c>
       <c r="I144" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J144" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K144" s="7">
         <v>5</v>
@@ -12893,16 +12461,13 @@
         <v>5</v>
       </c>
       <c r="M144" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N144" s="7">
-        <v>4</v>
-      </c>
-      <c r="O144" s="7">
         <v>0.93333333333333335</v>
       </c>
     </row>
-    <row r="145" spans="1:15">
+    <row r="145" spans="1:14">
       <c r="A145" s="7">
         <v>3</v>
       </c>
@@ -12916,36 +12481,33 @@
         <v>13</v>
       </c>
       <c r="E145" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="F145" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="F145" s="7">
-        <v>0</v>
-      </c>
       <c r="G145" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="H145" s="7" t="s">
         <v>28</v>
       </c>
+      <c r="H145" s="7">
+        <v>4</v>
+      </c>
       <c r="I145" s="7">
         <v>4</v>
       </c>
       <c r="J145" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K145" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L145" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M145" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N145" s="7">
-        <v>4</v>
-      </c>
-      <c r="O145" s="7">
         <v>0.8666666666666667</v>
       </c>
     </row>
